--- a/artfynd/A 29183-2025 artfynd.xlsx
+++ b/artfynd/A 29183-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74947980</v>
       </c>
       <c r="B2" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567037.0734594846</v>
+        <v>567037</v>
       </c>
       <c r="R2" t="n">
-        <v>6395534.130033151</v>
+        <v>6395534</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 29183-2025 artfynd.xlsx
+++ b/artfynd/A 29183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74947980</v>
       </c>
       <c r="B2" t="n">
-        <v>110704</v>
+        <v>110713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29183-2025 artfynd.xlsx
+++ b/artfynd/A 29183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74947980</v>
       </c>
       <c r="B2" t="n">
-        <v>110713</v>
+        <v>110718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29183-2025 artfynd.xlsx
+++ b/artfynd/A 29183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74947980</v>
       </c>
       <c r="B2" t="n">
-        <v>110718</v>
+        <v>110746</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29183-2025 artfynd.xlsx
+++ b/artfynd/A 29183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74947980</v>
       </c>
       <c r="B2" t="n">
-        <v>110746</v>
+        <v>110752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29183-2025 artfynd.xlsx
+++ b/artfynd/A 29183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74947980</v>
       </c>
       <c r="B2" t="n">
-        <v>110752</v>
+        <v>110759</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29183-2025 artfynd.xlsx
+++ b/artfynd/A 29183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74947980</v>
       </c>
       <c r="B2" t="n">
-        <v>110759</v>
+        <v>110763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29183-2025 artfynd.xlsx
+++ b/artfynd/A 29183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74947980</v>
       </c>
       <c r="B2" t="n">
-        <v>110763</v>
+        <v>110771</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29183-2025 artfynd.xlsx
+++ b/artfynd/A 29183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74947980</v>
       </c>
       <c r="B2" t="n">
-        <v>110774</v>
+        <v>110779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29183-2025 artfynd.xlsx
+++ b/artfynd/A 29183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74947980</v>
       </c>
       <c r="B2" t="n">
-        <v>110779</v>
+        <v>110787</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29183-2025 artfynd.xlsx
+++ b/artfynd/A 29183-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74947980</v>
       </c>
       <c r="B2" t="n">
-        <v>110787</v>
+        <v>110797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29183-2025 artfynd.xlsx
+++ b/artfynd/A 29183-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>74947980</v>
       </c>
       <c r="B2" t="n">
-        <v>110797</v>
+        <v>111389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
